--- a/docs/config_template.xlsx
+++ b/docs/config_template.xlsx
@@ -233,11 +233,18 @@
     </comment>
     <comment ref="B4" authorId="0" shapeId="0">
       <text>
+        <t>Naam of BRIN-code van de instelling. Optioneel.
+Wordt gebruikt als label in het dashboard en het rapport.
+Voorbeelden: Radboud Universiteit, 21RI</t>
+      </text>
+    </comment>
+    <comment ref="B5" authorId="0" shapeId="0">
+      <text>
         <t>Het selectiejaar.
 Voorbeelden: 2025, 2026</t>
       </text>
     </comment>
-    <comment ref="B5" authorId="0" shapeId="0">
+    <comment ref="B6" authorId="0" shapeId="0">
       <text>
         <t>De exacte naam van het tabblad (sheet) in je selectiebestand waar de data staat.
 Open je bestand en kijk onderin welke tabbladen er zijn.
@@ -247,7 +254,7 @@
 - 2 Master beoordelingen</t>
       </text>
     </comment>
-    <comment ref="B6" authorId="0" shapeId="0">
+    <comment ref="B7" authorId="0" shapeId="0">
       <text>
         <t>Het rijnummer waarop de kolomnamen staan.
 Meestal is dit 1.
@@ -255,7 +262,7 @@
 Voorbeelden: 1, 3</t>
       </text>
     </comment>
-    <comment ref="B7" authorId="0" shapeId="0">
+    <comment ref="B8" authorId="0" shapeId="0">
       <text>
         <t>De exacte kolomnaam van de definitieve totaalscore.
 Dit is de score waarop de ranglijst is gebaseerd.
@@ -264,24 +271,6 @@
 - TOTAALSCORE
 - C_Sc_Totaal
 - Totale selectiescore %</t>
-      </text>
-    </comment>
-    <comment ref="B8" authorId="0" shapeId="0">
-      <text>
-        <t>De exacte kolomnaam van het definitieve rangnummer.
-Voorbeelden:
-- Rangnummer definitief
-- Rangnummer
-- Uiteindelijke rangnummer master FMC 26-27</t>
-      </text>
-    </comment>
-    <comment ref="B9" authorId="0" shapeId="0">
-      <text>
-        <t>De kolomnaam van het willekeurig rangnummer bij gelijke scores.
-Laat LEEG als er geen loting is.
-Voorbeelden:
-- Random rangnummer
-- Random rangnummer bepaald 13-04-2026</t>
       </text>
     </comment>
   </commentList>
@@ -761,137 +750,115 @@
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="5" t="inlineStr">
         <is>
+          <t>instellingscode</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Naam of BRIN-code van de instelling. Wordt label in het dashboard en het rapport.</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Radboud Universiteit
+21RI</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Optioneel.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
           <t>jaar</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>Het selectiejaar.</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>2025
 2026</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Het jaar waarin de selectie plaatsvond.</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+    <row r="11" ht="45" customHeight="1">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>blad_naam</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>De exacte naam van het tabblad (sheet) in het selectiebestand.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>2026 LUMC Farmacie
 Scores en ranking</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Open je bestand en kijk onderin naar de tabbladen.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>header_rij</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>Rijnummer waarop de kolomnamen staan. Meestal 1.</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>1
 3</t>
         </is>
       </c>
-      <c r="D11" s="5" t="inlineStr">
+      <c r="D12" s="6" t="inlineStr">
         <is>
           <t>Soms staat er een groepskop boven de kolomnamen, dan is het 2 of 3.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>totaalscore_kolom</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>De exacte kolomnaam van de definitieve totaalscore.</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>TOTAALSCORE
 C_Sc_Totaal</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Dit is een uitkomst, geen los item.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>rangnummer_kolom</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>De exacte kolomnaam van het definitieve rangnummer.</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Rangnummer definitief
-Rangnummer</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Het uiteindelijke rangnummer na eventuele loting.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>loting_kolom</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Kolomnaam van het lotingsrangnummer. Leeg als niet van toepassing.</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>Random rangnummer</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>Niet elk bestand heeft loting.</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1047,7 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>2. Totaalscore en rangnummer staan in de instellingen, niet in het kolommen-tabblad. Ze zijn uitkomsten, geen losse items.</t>
+          <t>2. De totaalscore staat in de instellingen en krijgt in het kolommen-tabblad ONWAAR. Het is een uitkomst, geen los item.</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1176,7 +1143,7 @@
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
-          <t>jaar</t>
+          <t>instellingscode</t>
         </is>
       </c>
       <c r="B4" s="8" t="n"/>
@@ -1184,7 +1151,7 @@
     <row r="5" ht="28" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>blad_naam</t>
+          <t>jaar</t>
         </is>
       </c>
       <c r="B5" s="8" t="n"/>
@@ -1192,38 +1159,30 @@
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>header_rij</t>
-        </is>
-      </c>
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>blad_naam</t>
+        </is>
+      </c>
+      <c r="B6" s="8" t="n"/>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>totaalscore_kolom</t>
-        </is>
-      </c>
-      <c r="B7" s="8" t="n"/>
+          <t>header_rij</t>
+        </is>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>rangnummer_kolom</t>
+          <t>totaalscore_kolom</t>
         </is>
       </c>
       <c r="B8" s="8" t="n"/>
-    </row>
-    <row r="9" ht="28" customHeight="1">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>loting_kolom</t>
-        </is>
-      </c>
-      <c r="B9" s="8" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
